--- a/medpilot-core/database.xlsx
+++ b/medpilot-core/database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,6 +1642,190 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CASE_88EE807E</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-22 11:24:40</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BS_01</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bệnh nhân mới</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thiếu thông tin: burning, allergy_update, previous_treatment (tên thuốc cụ thể)</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>approved_by_doctor</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CASE_D3AFCE4E</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-22 20:18:07</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BS_01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bệnh nhân mới</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thiếu thông tin: burning, allergy_update, previous_treatment (tên thuốc cụ thể)</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>approved_by_doctor</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CASE_3D94CAF8</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-22 20:18:24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BS_01</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bệnh nhân mới</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thiếu thông tin: burning, allergy_update, previous_treatment (tên thuốc cụ thể)</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>approved_by_doctor</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CASE_C6767D06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-22 20:18:58</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BS_01</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Trần Thị Bình</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>34</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Thiếu thông tin: burning, allergy_update, previous_treatment (tên thuốc cụ thể)</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>approved_by_doctor</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
